--- a/Data/RemapDrafts/XianglingRemapDraft.xlsx
+++ b/Data/RemapDrafts/XianglingRemapDraft.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB34FEA-ACC7-4826-9F76-7F6C38F99E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62096884-EBB3-4646-96E3-1650EC397CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{F8BD3DC3-F6C2-4809-8B31-A9D12C142664}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="V5.3 - Xiangling to Cheer" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V5.3 - Xiangling to Cheer'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V5.3 - Xiangling to Cheer'!$A$1:$D$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1304,10 +1304,11 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{0A8DBCD4-58C9-4D83-BA94-EBBD7745B45F}"/>
+  <autoFilter ref="A1:D78" xr:uid="{0A8DBCD4-58C9-4D83-BA94-EBBD7745B45F}"/>
   <conditionalFormatting sqref="B2:B78">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data/RemapDrafts/XianglingRemapDraft.xlsx
+++ b/Data/RemapDrafts/XianglingRemapDraft.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62096884-EBB3-4646-96E3-1650EC397CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21633F7-01F5-4F04-9D8B-167772B42506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{F8BD3DC3-F6C2-4809-8B31-A9D12C142664}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{F8BD3DC3-F6C2-4809-8B31-A9D12C142664}"/>
   </bookViews>
   <sheets>
     <sheet name="V5.3 - Xiangling to Cheer" sheetId="1" r:id="rId1"/>
+    <sheet name="V5.3 - Cheer to Xiangling" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V5.3 - Cheer to Xiangling'!$A$1:$D$99</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V5.3 - Xiangling to Cheer'!$A$1:$D$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -132,6 +134,90 @@
   </si>
   <si>
     <t>Xiangling's top front dress</t>
+  </si>
+  <si>
+    <t>XianglingCheer's pompom behind back</t>
+  </si>
+  <si>
+    <t>XianglingCheer's front purse strap</t>
+  </si>
+  <si>
+    <t>XianglingCheer's right wrist</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left wrist</t>
+  </si>
+  <si>
+    <t>XianglingCheer's right ponytail</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left ponytail</t>
+  </si>
+  <si>
+    <t>XianglingCheer's jacket top left front</t>
+  </si>
+  <si>
+    <t>XianglingCheer's jacket top right back</t>
+  </si>
+  <si>
+    <t>XianglingCheer's jacket top back</t>
+  </si>
+  <si>
+    <t>XianglingCheer's jacket top left back</t>
+  </si>
+  <si>
+    <t>XianglingCheer's jacket top right front</t>
+  </si>
+  <si>
+    <t>XianglingCheer's jacket top right</t>
+  </si>
+  <si>
+    <t>XianglingCheer's jacket top left</t>
+  </si>
+  <si>
+    <t>XianglingCheer's right knee</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left knee</t>
+  </si>
+  <si>
+    <t>XianglingCheer's right jacket back wing</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left jacket back wing</t>
+  </si>
+  <si>
+    <t>XianglingCheer's right sleeve</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left sleeve</t>
+  </si>
+  <si>
+    <t>XianglingCheer's right upper arm</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left upper arm</t>
+  </si>
+  <si>
+    <t>XianglingCheer's right calf</t>
+  </si>
+  <si>
+    <t>XianglingCheer's right shoulder</t>
+  </si>
+  <si>
+    <t>XianglingCheer's right middle arm</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left calf</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left shoulder</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left thigh</t>
+  </si>
+  <si>
+    <t>XianglingCheer's left middle arm</t>
   </si>
 </sst>
 </file>
@@ -182,7 +268,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -1306,9 +1402,926 @@
   </sheetData>
   <autoFilter ref="A1:D78" xr:uid="{0A8DBCD4-58C9-4D83-BA94-EBBD7745B45F}"/>
   <conditionalFormatting sqref="B2:B78">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D593CF-0CC8-4EDB-8227-6A3E8D7A9BBE}">
+  <dimension ref="A1:D99"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>65</v>
+      </c>
+      <c r="C2">
+        <v>0.2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0.2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0.2</v>
+      </c>
+      <c r="D16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>65</v>
+      </c>
+      <c r="C18">
+        <v>0.3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>16</v>
+      </c>
+      <c r="D26" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>16</v>
+      </c>
+      <c r="D28" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>18</v>
+      </c>
+      <c r="D33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>65</v>
+      </c>
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>65</v>
+      </c>
+      <c r="D37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="D39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>20</v>
+      </c>
+      <c r="D40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>59</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>56</v>
+      </c>
+      <c r="D47" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>58</v>
+      </c>
+      <c r="D51" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>55</v>
+      </c>
+      <c r="D72" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>9</v>
+      </c>
+      <c r="D74" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>57</v>
+      </c>
+      <c r="D75" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>18</v>
+      </c>
+      <c r="D94" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>37</v>
+      </c>
+      <c r="D96" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D99" xr:uid="{26D593CF-0CC8-4EDB-8227-6A3E8D7A9BBE}"/>
+  <conditionalFormatting sqref="B2:B99">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/RemapDrafts/XianglingRemapDraft.xlsx
+++ b/Data/RemapDrafts/XianglingRemapDraft.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21633F7-01F5-4F04-9D8B-167772B42506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3BD051-AF54-4DE2-88C0-89DA9EE323BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{F8BD3DC3-F6C2-4809-8B31-A9D12C142664}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{F8BD3DC3-F6C2-4809-8B31-A9D12C142664}"/>
   </bookViews>
   <sheets>
     <sheet name="V5.3 - Xiangling to Cheer" sheetId="1" r:id="rId1"/>
@@ -2323,5 +2323,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Data/RemapDrafts/XianglingRemapDraft.xlsx
+++ b/Data/RemapDrafts/XianglingRemapDraft.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3BD051-AF54-4DE2-88C0-89DA9EE323BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92BF6B7-6EDC-4A0B-B460-3DF0E91259EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{F8BD3DC3-F6C2-4809-8B31-A9D12C142664}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{F8BD3DC3-F6C2-4809-8B31-A9D12C142664}"/>
   </bookViews>
   <sheets>
-    <sheet name="V5.3 - Xiangling to Cheer" sheetId="1" r:id="rId1"/>
-    <sheet name="V5.3 - Cheer to Xiangling" sheetId="2" r:id="rId2"/>
+    <sheet name="Credits" sheetId="3" r:id="rId1"/>
+    <sheet name="V5.3 - Xiangling to Cheer" sheetId="1" r:id="rId2"/>
+    <sheet name="V5.3 - Cheer to Xiangling" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V5.3 - Cheer to Xiangling'!$A$1:$D$99</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V5.3 - Xiangling to Cheer'!$A$1:$D$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V5.3 - Cheer to Xiangling'!$A$1:$D$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V5.3 - Xiangling to Cheer'!$A$1:$D$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -218,13 +219,22 @@
   </si>
   <si>
     <t>XianglingCheer's left middle arm</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +245,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -258,14 +284,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -618,6 +648,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBFABD64-2602-49EF-88AE-5AE1DF31EBCE}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{CEC9F004-61F0-463E-990E-BC0998044956}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8DBCD4-58C9-4D83-BA94-EBBD7745B45F}">
   <dimension ref="A1:D78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1409,7 +1470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D593CF-0CC8-4EDB-8227-6A3E8D7A9BBE}">
   <dimension ref="A1:D99"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
